--- a/CBS.FrontDesk.UI/AppFiles/ShareMonthUpload/Unprocessed data.xlsx
+++ b/CBS.FrontDesk.UI/AppFiles/ShareMonthUpload/Unprocessed data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDB0B8D7-6A9F-4689-871B-7F9BA42363A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A44882C-6306-45C1-A39A-B757263BE61E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A06C77E9-8964-4E85-A58B-00255449579B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{A06C77E9-8964-4E85-A58B-00255449579B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
-  <si>
-    <t>BAPCCUL</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="28">
   <si>
     <t xml:space="preserve">Branch Name : </t>
   </si>
   <si>
-    <t>Biyem-Assi</t>
-  </si>
-  <si>
     <t xml:space="preserve">Branch Code : </t>
   </si>
   <si>
@@ -106,6 +100,15 @@
   </si>
   <si>
     <t>December</t>
+  </si>
+  <si>
+    <t>Affiliate</t>
+  </si>
+  <si>
+    <t>Branch Name</t>
+  </si>
+  <si>
+    <t>branch code</t>
   </si>
 </sst>
 </file>
@@ -261,7 +264,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -271,11 +274,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -289,17 +299,9 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -624,117 +626,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="21" x14ac:dyDescent="0.4">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="14"/>
+      <c r="A1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="17"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="11"/>
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="14"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="15">
-        <v>3</v>
-      </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="11"/>
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="16">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18">
         <v>46022</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="11"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="11"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="15">
-        <v>1000</v>
-      </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="11"/>
+        <v>4</v>
+      </c>
+      <c r="B6" s="13">
+        <v>10</v>
+      </c>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="11"/>
+        <v>21</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="10"/>
+      <c r="A8" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="12"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="E9" s="3" t="s">
         <v>10</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>1</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="19">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10">
         <v>10000</v>
       </c>
       <c r="E10" s="5">
@@ -745,13 +747,13 @@
       <c r="A11" s="4">
         <v>2</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="19">
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11">
         <v>15000</v>
       </c>
       <c r="E11" s="5">
@@ -762,13 +764,13 @@
       <c r="A12" s="4">
         <v>3</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="19">
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12">
         <v>4000</v>
       </c>
       <c r="E12" s="5">
@@ -779,13 +781,13 @@
       <c r="A13" s="4">
         <v>4</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="19">
+      <c r="B13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13">
         <v>5000</v>
       </c>
       <c r="E13" s="5">
@@ -796,13 +798,13 @@
       <c r="A14" s="4">
         <v>5</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="19">
+      <c r="B14" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14">
         <v>600000</v>
       </c>
       <c r="E14" s="5">
@@ -813,13 +815,13 @@
       <c r="A15" s="4">
         <v>6</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="19">
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>24</v>
+      </c>
+      <c r="D15">
         <v>450000</v>
       </c>
       <c r="E15" s="5">
@@ -830,13 +832,13 @@
       <c r="A16" s="4">
         <v>7</v>
       </c>
-      <c r="B16" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="19">
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16">
         <v>90000</v>
       </c>
       <c r="E16" s="5">
@@ -847,13 +849,13 @@
       <c r="A17" s="4">
         <v>8</v>
       </c>
-      <c r="B17" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="19">
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17">
         <v>670000</v>
       </c>
       <c r="E17" s="5">
@@ -864,13 +866,13 @@
       <c r="A18" s="4">
         <v>9</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="19">
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18">
         <v>34000</v>
       </c>
       <c r="E18" s="5">
@@ -882,10 +884,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D19" s="7">
         <v>65000</v>
